--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67684_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67684_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7f44848f435448b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re0bdefd84f574e2d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67684_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67684_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re0bdefd84f574e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1a1a67512f364b2e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.4298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.3275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.4298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.3275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.3275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.6267</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.0282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.3351</x:v>
+        <x:v>     23.1229</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,13 +1644,2443 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     23.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.8313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.3275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.6267</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     21.0282</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>09/07/2026</x:t>
+          <x:t>31/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.5244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.0282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.5091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.5015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.2022</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.3045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.3045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.5015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.7854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.8877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.7854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.1946</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.5015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.4785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.1716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.2816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.6831</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.3839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.7930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.7930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.7854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.0617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.0617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.6602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.4632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.8647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.8724</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.0770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.2816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.4785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.2739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.4709</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.4632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.4632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.9517</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.0387</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.2357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.8265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.8265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1334</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.8341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.5426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.2433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.7395</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.8341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.7318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.8265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.6219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.8188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.4173</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.5349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.8188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.0158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.8265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.7165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.8112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.6219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.0311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.0081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.3150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.4097</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.2127</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.1104</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.8188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.4020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     73.9928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.3867</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.4661</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.7959</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.8112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.2357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.2280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.5196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.5349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.2051</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.1257</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.7395</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.6372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7061</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.3045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.3045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.5015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.5015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.6984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.4862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.1869</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.4632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.8341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.6372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.6908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/01/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -945,2212 +4095,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5168</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     20.7290</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5168</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     19.8313</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.5244</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     21.3275</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.6191</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     21.6267</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     21.9259</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     20.7290</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.5244</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.5244</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.4221</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     21.9259</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.9183</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.7214</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.3198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.0206</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.2252</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.7214</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.8236</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.3198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.8236</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.2252</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.5244</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.8236</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     21.0282</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.5244</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.6191</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.8236</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1152</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.1229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5168</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.8236</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.3198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     21.0282</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.0206</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.0206</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.3198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5168</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5168</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.5091</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.0206</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.5015</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.0053</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.2022</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.9106</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.0999</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.3045</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.0999</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.3045</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     35.9900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.5015</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.7854</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     36.8877</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.7854</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     34.1946</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.5015</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     40.4785</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     43.1716</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.2816</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     38.6831</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     38.3839</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     34.7930</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     34.7930</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.7854</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     35.9900</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     47.0617</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     47.0617</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     47.6602</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     46.4632</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     45.8647</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     42.8724</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     41.0770</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.8800</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.2816</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     40.4785</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     42.2739</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     43.4709</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     46.4632</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     46.4632</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     50.9517</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     56.0387</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.2357</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     60.8265</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     60.8265</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     58.1334</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.8341</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     54.5426</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     54.2433</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     55.7395</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.8341</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     58.7318</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     60.8265</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.6219</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     63.8188</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     64.4173</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.5349</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.5120</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     63.8188</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     65.0158</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     59.9288</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     60.8265</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     64.7165</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.8112</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.5120</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.6219</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     59.0311</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.4250</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     68.0081</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     65.3150</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.4250</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.4250</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     67.4097</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.2127</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     67.1104</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     63.8188</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     70.4020</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     73.9928</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     76.3867</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     84.4661</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     72.7959</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.8112</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.4250</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.2357</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     60.2280</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     63.5196</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.5349</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     69.2051</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.1257</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     55.7395</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     56.6372</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     35.3915</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.7061</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.3045</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/02/2026</x:t>
+          <x:t>27/01/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -3165,52 +4110,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>10/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.3045</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.5015</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.5015</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/02/2026</x:t>
+          <x:t>26/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/01/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -3220,201 +4135,6 @@
       </x:c>
       <x:c s="3">
         <x:v>     32.6984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.4862</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.1869</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     46.4632</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.8341</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     56.6372</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     35.6908</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5168</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.7214</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.9030</x:v>
       </x:c>
     </x:row>
     <x:row>
